--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/65.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/65.xlsx
@@ -426,13 +426,13 @@
         <v>-18.29353546314387</v>
       </c>
       <c r="E2">
-        <v>-16.75652877985591</v>
+        <v>-15.6311305333657</v>
       </c>
       <c r="F2">
-        <v>3.941922819595402</v>
+        <v>1.574558126891584</v>
       </c>
       <c r="G2">
-        <v>-12.89733241604829</v>
+        <v>-14.57224672656386</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-17.58686842742348</v>
       </c>
       <c r="E3">
-        <v>-15.55056898076925</v>
+        <v>-17.05630923068968</v>
       </c>
       <c r="F3">
-        <v>4.292593935487711</v>
+        <v>2.638659011710162</v>
       </c>
       <c r="G3">
-        <v>-12.7974028134554</v>
+        <v>-13.79799164067871</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-16.78687274679731</v>
       </c>
       <c r="E4">
-        <v>-16.49816575229629</v>
+        <v>-19.57892737598051</v>
       </c>
       <c r="F4">
-        <v>3.974724512011456</v>
+        <v>1.878668367807339</v>
       </c>
       <c r="G4">
-        <v>-11.62102910362796</v>
+        <v>-13.47736051355445</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-15.96628525869283</v>
       </c>
       <c r="E5">
-        <v>-16.37172622952813</v>
+        <v>-19.83961351070606</v>
       </c>
       <c r="F5">
-        <v>3.580993201786824</v>
+        <v>2.505760715809426</v>
       </c>
       <c r="G5">
-        <v>-10.83048439331094</v>
+        <v>-13.43633868161827</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-15.1356652135631</v>
       </c>
       <c r="E6">
-        <v>-16.87899683091935</v>
+        <v>-19.67084181291419</v>
       </c>
       <c r="F6">
-        <v>3.758434469670894</v>
+        <v>2.397668710152924</v>
       </c>
       <c r="G6">
-        <v>-10.74243937520636</v>
+        <v>-12.04862477236856</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-14.32327288927612</v>
       </c>
       <c r="E7">
-        <v>-17.87534262513897</v>
+        <v>-20.54874084098918</v>
       </c>
       <c r="F7">
-        <v>3.951054741843863</v>
+        <v>2.384053663520511</v>
       </c>
       <c r="G7">
-        <v>-11.24889264168509</v>
+        <v>-12.36084612863596</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-13.54359400945425</v>
       </c>
       <c r="E8">
-        <v>-18.31967196629757</v>
+        <v>-20.1732080769551</v>
       </c>
       <c r="F8">
-        <v>2.980776405801163</v>
+        <v>2.105617841887125</v>
       </c>
       <c r="G8">
-        <v>-9.651666173421715</v>
+        <v>-11.55922401433426</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.8170172551798</v>
       </c>
       <c r="E9">
-        <v>-18.22501780258925</v>
+        <v>-19.87029845058203</v>
       </c>
       <c r="F9">
-        <v>3.615054012655134</v>
+        <v>1.985476403989501</v>
       </c>
       <c r="G9">
-        <v>-9.684005893111602</v>
+        <v>-11.75243874586216</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.15529637455975</v>
       </c>
       <c r="E10">
-        <v>-19.20099452072236</v>
+        <v>-20.68186891986668</v>
       </c>
       <c r="F10">
-        <v>3.730347844511574</v>
+        <v>1.976387556845985</v>
       </c>
       <c r="G10">
-        <v>-8.710601986508292</v>
+        <v>-9.979552081413907</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.56622507980704</v>
       </c>
       <c r="E11">
-        <v>-20.3852131160982</v>
+        <v>-21.31008600505475</v>
       </c>
       <c r="F11">
-        <v>3.707259588260746</v>
+        <v>1.947343338969029</v>
       </c>
       <c r="G11">
-        <v>-8.472329520526095</v>
+        <v>-11.88264089856249</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.05327237235941</v>
       </c>
       <c r="E12">
-        <v>-22.26917151513926</v>
+        <v>-21.81026048767595</v>
       </c>
       <c r="F12">
-        <v>3.62227571967274</v>
+        <v>1.954192280655375</v>
       </c>
       <c r="G12">
-        <v>-7.456483013051368</v>
+        <v>-9.962814570239178</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.61404455142831</v>
       </c>
       <c r="E13">
-        <v>-22.76002639825267</v>
+        <v>-24.56743094419407</v>
       </c>
       <c r="F13">
-        <v>3.705708884482706</v>
+        <v>2.877081374318721</v>
       </c>
       <c r="G13">
-        <v>-7.134598459291401</v>
+        <v>-8.612903614575826</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.25878356729652</v>
       </c>
       <c r="E14">
-        <v>-21.90483313885214</v>
+        <v>-23.16151184682471</v>
       </c>
       <c r="F14">
-        <v>4.049323966837969</v>
+        <v>2.656642868024939</v>
       </c>
       <c r="G14">
-        <v>-6.763052617229238</v>
+        <v>-8.687846714993544</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.99079767039969</v>
       </c>
       <c r="E15">
-        <v>-23.43975940375201</v>
+        <v>-25.29321853035141</v>
       </c>
       <c r="F15">
-        <v>4.001513913817992</v>
+        <v>2.987761199741569</v>
       </c>
       <c r="G15">
-        <v>-6.798499653735919</v>
+        <v>-8.767836334169687</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.812038394554511</v>
       </c>
       <c r="E16">
-        <v>-24.84380371288219</v>
+        <v>-25.97736226953421</v>
       </c>
       <c r="F16">
-        <v>4.249187483581017</v>
+        <v>3.078639730767897</v>
       </c>
       <c r="G16">
-        <v>-6.028590545806252</v>
+        <v>-7.73838916333106</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.720411458093039</v>
       </c>
       <c r="E17">
-        <v>-25.30408233949581</v>
+        <v>-27.86357132015709</v>
       </c>
       <c r="F17">
-        <v>4.133549050885011</v>
+        <v>3.02165965059893</v>
       </c>
       <c r="G17">
-        <v>-5.437891915788776</v>
+        <v>-7.931003431313584</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.707133408543484</v>
       </c>
       <c r="E18">
-        <v>-24.73190512015265</v>
+        <v>-28.96663966131547</v>
       </c>
       <c r="F18">
-        <v>4.699638766610137</v>
+        <v>3.124281117927344</v>
       </c>
       <c r="G18">
-        <v>-4.745823226913815</v>
+        <v>-7.854839716475754</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.766912182377432</v>
       </c>
       <c r="E19">
-        <v>-26.11185794756203</v>
+        <v>-28.93468222024334</v>
       </c>
       <c r="F19">
-        <v>4.573753429141502</v>
+        <v>2.811577393574948</v>
       </c>
       <c r="G19">
-        <v>-5.241875021049109</v>
+        <v>-6.426215536822881</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.88934877298885</v>
       </c>
       <c r="E20">
-        <v>-28.07098901513042</v>
+        <v>-28.50277448328778</v>
       </c>
       <c r="F20">
-        <v>4.773838948348501</v>
+        <v>3.688742263338566</v>
       </c>
       <c r="G20">
-        <v>-5.044466888368236</v>
+        <v>-6.840023512570692</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-10.06730304402508</v>
       </c>
       <c r="E21">
-        <v>-28.35654100063208</v>
+        <v>-30.37345539653835</v>
       </c>
       <c r="F21">
-        <v>4.621593303387979</v>
+        <v>3.115409303043361</v>
       </c>
       <c r="G21">
-        <v>-4.140296756669209</v>
+        <v>-6.35897674462674</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-10.2910028897407</v>
       </c>
       <c r="E22">
-        <v>-29.40436195889689</v>
+        <v>-30.28471768412104</v>
       </c>
       <c r="F22">
-        <v>4.83916731520288</v>
+        <v>3.713308327035989</v>
       </c>
       <c r="G22">
-        <v>-3.376343065869934</v>
+        <v>-6.018412196528854</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-10.54941048951029</v>
       </c>
       <c r="E23">
-        <v>-29.01584605988282</v>
+        <v>-31.62343422721657</v>
       </c>
       <c r="F23">
-        <v>4.516776662442147</v>
+        <v>4.947731490278978</v>
       </c>
       <c r="G23">
-        <v>-3.559651789509873</v>
+        <v>-6.932238963277326</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-10.83343825169437</v>
       </c>
       <c r="E24">
-        <v>-29.53650962315172</v>
+        <v>-30.95926332264459</v>
       </c>
       <c r="F24">
-        <v>4.994289051785922</v>
+        <v>3.54833398856405</v>
       </c>
       <c r="G24">
-        <v>-2.847019685121872</v>
+        <v>-6.040042009048713</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-11.13105093009765</v>
       </c>
       <c r="E25">
-        <v>-30.04496668473295</v>
+        <v>-31.45358248837387</v>
       </c>
       <c r="F25">
-        <v>4.786174995710991</v>
+        <v>3.60492142258409</v>
       </c>
       <c r="G25">
-        <v>-2.576289375473648</v>
+        <v>-5.768934358921154</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-11.43792285923395</v>
       </c>
       <c r="E26">
-        <v>-30.12437574069445</v>
+        <v>-32.36073545853841</v>
       </c>
       <c r="F26">
-        <v>5.113623659833219</v>
+        <v>4.203408587432705</v>
       </c>
       <c r="G26">
-        <v>-2.629251572664645</v>
+        <v>-4.697950204361518</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-11.74521447667839</v>
       </c>
       <c r="E27">
-        <v>-30.76300831610017</v>
+        <v>-31.85653063405039</v>
       </c>
       <c r="F27">
-        <v>5.053229049229912</v>
+        <v>5.056646893133863</v>
       </c>
       <c r="G27">
-        <v>-1.763084549067107</v>
+        <v>-4.632059994226307</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-12.0437977440352</v>
       </c>
       <c r="E28">
-        <v>-31.39825359294815</v>
+        <v>-29.86442774723215</v>
       </c>
       <c r="F28">
-        <v>5.53174541986588</v>
+        <v>4.285244659890074</v>
       </c>
       <c r="G28">
-        <v>-1.301633236276159</v>
+        <v>-4.99805729063145</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-12.32126234945691</v>
       </c>
       <c r="E29">
-        <v>-29.26531516449137</v>
+        <v>-33.10756007069839</v>
       </c>
       <c r="F29">
-        <v>4.997201591574164</v>
+        <v>3.938879397757516</v>
       </c>
       <c r="G29">
-        <v>-2.523235304078986</v>
+        <v>-5.728191430817528</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-12.56811546896066</v>
       </c>
       <c r="E30">
-        <v>-29.84657197421991</v>
+        <v>-30.96504618395238</v>
       </c>
       <c r="F30">
-        <v>5.082689107543073</v>
+        <v>4.419967020811774</v>
       </c>
       <c r="G30">
-        <v>-1.523201003299223</v>
+        <v>-5.041330040557407</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-12.77712119107646</v>
       </c>
       <c r="E31">
-        <v>-29.68567529272738</v>
+        <v>-30.23706455213833</v>
       </c>
       <c r="F31">
-        <v>5.138814312552351</v>
+        <v>3.882074931477943</v>
       </c>
       <c r="G31">
-        <v>-2.506081077766209</v>
+        <v>-4.686022963992936</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-12.94159121054684</v>
       </c>
       <c r="E32">
-        <v>-29.6073440135797</v>
+        <v>-30.2426549533008</v>
       </c>
       <c r="F32">
-        <v>4.607840747766701</v>
+        <v>4.247961499824873</v>
       </c>
       <c r="G32">
-        <v>-2.303560801895722</v>
+        <v>-3.847552731578671</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-13.05535644837951</v>
       </c>
       <c r="E33">
-        <v>-30.32613057892119</v>
+        <v>-29.68009621274993</v>
       </c>
       <c r="F33">
-        <v>4.937390151622429</v>
+        <v>3.621909581280702</v>
       </c>
       <c r="G33">
-        <v>-3.418631449328057</v>
+        <v>-3.505167105515293</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-13.11159435898489</v>
       </c>
       <c r="E34">
-        <v>-29.03881900852373</v>
+        <v>-29.44863005655887</v>
       </c>
       <c r="F34">
-        <v>5.273541643678469</v>
+        <v>4.070798563388143</v>
       </c>
       <c r="G34">
-        <v>-2.898928610192288</v>
+        <v>-4.543155296073153</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-13.11036173406913</v>
       </c>
       <c r="E35">
-        <v>-29.31016517106334</v>
+        <v>-29.43100749995802</v>
       </c>
       <c r="F35">
-        <v>4.733659815843113</v>
+        <v>3.560547437550926</v>
       </c>
       <c r="G35">
-        <v>-2.466457046214355</v>
+        <v>-4.051152529342215</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-13.05289377397337</v>
       </c>
       <c r="E36">
-        <v>-28.90497995922703</v>
+        <v>-28.68517688784273</v>
       </c>
       <c r="F36">
-        <v>5.037700473897033</v>
+        <v>4.172954488236184</v>
       </c>
       <c r="G36">
-        <v>-2.541393584188953</v>
+        <v>-4.559266093930026</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-12.94704052434615</v>
       </c>
       <c r="E37">
-        <v>-28.86402444030166</v>
+        <v>-28.39155063318538</v>
       </c>
       <c r="F37">
-        <v>4.849702491831684</v>
+        <v>3.882969568272967</v>
       </c>
       <c r="G37">
-        <v>-3.871896114328191</v>
+        <v>-5.072560707360202</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-12.80122259107784</v>
       </c>
       <c r="E38">
-        <v>-26.62851154709714</v>
+        <v>-28.31490621060556</v>
       </c>
       <c r="F38">
-        <v>5.164258445696741</v>
+        <v>3.873073891279124</v>
       </c>
       <c r="G38">
-        <v>-3.030833716881965</v>
+        <v>-6.035471267416407</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-12.62362980933291</v>
       </c>
       <c r="E39">
-        <v>-28.45122233518446</v>
+        <v>-27.50463541336112</v>
       </c>
       <c r="F39">
-        <v>5.659078743554609</v>
+        <v>4.033097906151932</v>
       </c>
       <c r="G39">
-        <v>-3.395311807705084</v>
+        <v>-5.868312716292055</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-12.42479542425822</v>
       </c>
       <c r="E40">
-        <v>-26.8877893264063</v>
+        <v>-27.62389730482713</v>
       </c>
       <c r="F40">
-        <v>5.270325921420801</v>
+        <v>4.519313123429519</v>
       </c>
       <c r="G40">
-        <v>-4.465633155509712</v>
+        <v>-6.550061963362563</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-12.21224176619662</v>
       </c>
       <c r="E41">
-        <v>-27.02037851687689</v>
+        <v>-26.13312366150205</v>
       </c>
       <c r="F41">
-        <v>5.390715869539264</v>
+        <v>4.764789862840319</v>
       </c>
       <c r="G41">
-        <v>-4.373506297785183</v>
+        <v>-5.42421906555057</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-11.9969741129024</v>
       </c>
       <c r="E42">
-        <v>-25.33402913810853</v>
+        <v>-26.10115263500789</v>
       </c>
       <c r="F42">
-        <v>5.270695373282449</v>
+        <v>4.386597068357399</v>
       </c>
       <c r="G42">
-        <v>-3.821529363390715</v>
+        <v>-5.876295928346185</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-11.78577678955875</v>
       </c>
       <c r="E43">
-        <v>-24.83320708370424</v>
+        <v>-21.77910458650318</v>
       </c>
       <c r="F43">
-        <v>5.662430318066336</v>
+        <v>4.343459007489211</v>
       </c>
       <c r="G43">
-        <v>-3.516871222817832</v>
+        <v>-7.410762471842065</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-11.58399113332082</v>
       </c>
       <c r="E44">
-        <v>-25.2092017520871</v>
+        <v>-24.05500693938212</v>
       </c>
       <c r="F44">
-        <v>5.528476682094433</v>
+        <v>4.146663763606133</v>
       </c>
       <c r="G44">
-        <v>-4.593190643633125</v>
+        <v>-6.119861004703766</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-11.39270459493934</v>
       </c>
       <c r="E45">
-        <v>-24.18712969702991</v>
+        <v>-25.52179778436258</v>
       </c>
       <c r="F45">
-        <v>5.826271449931244</v>
+        <v>4.324887010318447</v>
       </c>
       <c r="G45">
-        <v>-4.656698686916179</v>
+        <v>-7.588617805250207</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-11.2167602535067</v>
       </c>
       <c r="E46">
-        <v>-22.49719376684748</v>
+        <v>-23.22624638276436</v>
       </c>
       <c r="F46">
-        <v>5.928863096033157</v>
+        <v>4.522936402449363</v>
       </c>
       <c r="G46">
-        <v>-4.775547813020825</v>
+        <v>-6.527113099775806</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-11.05913326116401</v>
       </c>
       <c r="E47">
-        <v>-22.99830564358827</v>
+        <v>-22.62150037835804</v>
       </c>
       <c r="F47">
-        <v>5.877595437473896</v>
+        <v>4.126534435718105</v>
       </c>
       <c r="G47">
-        <v>-5.520362138463859</v>
+        <v>-6.534853501434537</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-10.91971129831727</v>
       </c>
       <c r="E48">
-        <v>-22.44928704032034</v>
+        <v>-24.27645384683121</v>
       </c>
       <c r="F48">
-        <v>6.003583492500479</v>
+        <v>4.529725701682708</v>
       </c>
       <c r="G48">
-        <v>-5.569826553472489</v>
+        <v>-7.523944928313552</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-10.79592181234269</v>
       </c>
       <c r="E49">
-        <v>-22.1902628555556</v>
+        <v>-21.25554053563237</v>
       </c>
       <c r="F49">
-        <v>5.773984899466539</v>
+        <v>5.046179642632088</v>
       </c>
       <c r="G49">
-        <v>-6.679863807032636</v>
+        <v>-7.597834756610687</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-10.67982824533046</v>
       </c>
       <c r="E50">
-        <v>-20.59432446035039</v>
+        <v>-21.35471411640034</v>
       </c>
       <c r="F50">
-        <v>6.421009423914788</v>
+        <v>5.023096356585677</v>
       </c>
       <c r="G50">
-        <v>-5.868424277825077</v>
+        <v>-7.417908972398536</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-10.56964362236533</v>
       </c>
       <c r="E51">
-        <v>-20.78404035042773</v>
+        <v>-19.42565211624289</v>
       </c>
       <c r="F51">
-        <v>5.790737801820756</v>
+        <v>4.425164197896938</v>
       </c>
       <c r="G51">
-        <v>-4.600419174728582</v>
+        <v>-6.329104503549555</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-10.46085351617854</v>
       </c>
       <c r="E52">
-        <v>-19.29888654334617</v>
+        <v>-22.21521927581188</v>
       </c>
       <c r="F52">
-        <v>6.126276301998725</v>
+        <v>4.524293268255149</v>
       </c>
       <c r="G52">
-        <v>-6.272224527816581</v>
+        <v>-7.458340184454014</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.35144707898411</v>
       </c>
       <c r="E53">
-        <v>-20.31243601032093</v>
+        <v>-18.46744060164187</v>
       </c>
       <c r="F53">
-        <v>6.096831154298813</v>
+        <v>5.075276876022824</v>
       </c>
       <c r="G53">
-        <v>-6.294615583738232</v>
+        <v>-8.095556692519738</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-10.23876599168401</v>
       </c>
       <c r="E54">
-        <v>-17.84588943019308</v>
+        <v>-17.87325952709543</v>
       </c>
       <c r="F54">
-        <v>5.950360886870611</v>
+        <v>4.394161719479763</v>
       </c>
       <c r="G54">
-        <v>-6.196342998032863</v>
+        <v>-7.905869274168238</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-10.11914809870813</v>
       </c>
       <c r="E55">
-        <v>-17.35090457878467</v>
+        <v>-15.81561603596419</v>
       </c>
       <c r="F55">
-        <v>6.550259589773595</v>
+        <v>4.298848109378847</v>
       </c>
       <c r="G55">
-        <v>-5.726124261235078</v>
+        <v>-8.640859622262294</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.993431756699664</v>
       </c>
       <c r="E56">
-        <v>-16.26025784182933</v>
+        <v>-17.15057394563335</v>
       </c>
       <c r="F56">
-        <v>5.887184618528703</v>
+        <v>4.895966811278037</v>
       </c>
       <c r="G56">
-        <v>-6.778290610151299</v>
+        <v>-8.646864257716079</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.862372846998559</v>
       </c>
       <c r="E57">
-        <v>-17.67572749088086</v>
+        <v>-17.33820220919315</v>
       </c>
       <c r="F57">
-        <v>6.556924633896521</v>
+        <v>4.694199706243356</v>
       </c>
       <c r="G57">
-        <v>-6.652803572831895</v>
+        <v>-8.807601458248596</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.731189742708848</v>
       </c>
       <c r="E58">
-        <v>-15.86442845729287</v>
+        <v>-16.3842248177893</v>
       </c>
       <c r="F58">
-        <v>6.149369528453969</v>
+        <v>4.408997779663903</v>
       </c>
       <c r="G58">
-        <v>-6.668090784077348</v>
+        <v>-9.547920510155192</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.602858137131623</v>
       </c>
       <c r="E59">
-        <v>-15.30204179875429</v>
+        <v>-16.68162329129504</v>
       </c>
       <c r="F59">
-        <v>5.814218704220512</v>
+        <v>4.22406972719333</v>
       </c>
       <c r="G59">
-        <v>-7.423788921433061</v>
+        <v>-8.861843331847778</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.479665995626785</v>
       </c>
       <c r="E60">
-        <v>-15.45537140018</v>
+        <v>-17.782083231425</v>
       </c>
       <c r="F60">
-        <v>5.996794193267133</v>
+        <v>4.882134732386091</v>
       </c>
       <c r="G60">
-        <v>-6.334019773445603</v>
+        <v>-9.566895814433462</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.362583953880128</v>
       </c>
       <c r="E61">
-        <v>-14.38475410376059</v>
+        <v>-15.32136932581903</v>
       </c>
       <c r="F61">
-        <v>6.181861411461377</v>
+        <v>3.99634987142894</v>
       </c>
       <c r="G61">
-        <v>-7.027594543016349</v>
+        <v>-8.614458913595003</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.254692388505026</v>
       </c>
       <c r="E62">
-        <v>-14.57949659998644</v>
+        <v>-15.03858423793605</v>
       </c>
       <c r="F62">
-        <v>5.927217958371197</v>
+        <v>4.754693720934998</v>
       </c>
       <c r="G62">
-        <v>-6.383434970130841</v>
+        <v>-9.248702634927868</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.159751737056009</v>
       </c>
       <c r="E63">
-        <v>-14.28937991268504</v>
+        <v>-14.32448011471849</v>
       </c>
       <c r="F63">
-        <v>5.781503162014348</v>
+        <v>4.514286590029331</v>
       </c>
       <c r="G63">
-        <v>-7.500786066546991</v>
+        <v>-10.82214352810683</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.078998987185736</v>
       </c>
       <c r="E64">
-        <v>-14.35481636209588</v>
+        <v>-14.18968555740618</v>
       </c>
       <c r="F64">
-        <v>5.441728390938463</v>
+        <v>4.430281851711434</v>
       </c>
       <c r="G64">
-        <v>-7.451269151993411</v>
+        <v>-10.27188267258795</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.012653707381181</v>
       </c>
       <c r="E65">
-        <v>-13.46702714678813</v>
+        <v>-13.44921665851597</v>
       </c>
       <c r="F65">
-        <v>5.567454681865761</v>
+        <v>4.38286610157519</v>
       </c>
       <c r="G65">
-        <v>-7.015093088874865</v>
+        <v>-10.13591541360769</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.957410748304504</v>
       </c>
       <c r="E66">
-        <v>-15.0983646233113</v>
+        <v>-13.97466908304798</v>
       </c>
       <c r="F66">
-        <v>5.634814205591805</v>
+        <v>4.391322076022967</v>
       </c>
       <c r="G66">
-        <v>-7.188341587213546</v>
+        <v>-9.204475049528114</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.915123302192782</v>
       </c>
       <c r="E67">
-        <v>-13.09666590007081</v>
+        <v>-12.93606809786279</v>
       </c>
       <c r="F67">
-        <v>5.1914984793704</v>
+        <v>4.198121946668039</v>
       </c>
       <c r="G67">
-        <v>-7.526917715046408</v>
+        <v>-9.115307853650204</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.88540678484642</v>
       </c>
       <c r="E68">
-        <v>-13.77720044546951</v>
+        <v>-15.26185612041023</v>
       </c>
       <c r="F68">
-        <v>5.336820629578323</v>
+        <v>4.859392733709633</v>
       </c>
       <c r="G68">
-        <v>-7.067510603286994</v>
+        <v>-9.205045982079458</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.869596338858573</v>
       </c>
       <c r="E69">
-        <v>-14.83522405567359</v>
+        <v>-14.42688249745394</v>
       </c>
       <c r="F69">
-        <v>5.303881428173403</v>
+        <v>3.923019475463517</v>
       </c>
       <c r="G69">
-        <v>-6.372816937164478</v>
+        <v>-8.876786014829488</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.867359185790249</v>
       </c>
       <c r="E70">
-        <v>-13.15474357921918</v>
+        <v>-12.92926180142926</v>
       </c>
       <c r="F70">
-        <v>5.224780624880078</v>
+        <v>3.816163393971992</v>
       </c>
       <c r="G70">
-        <v>-6.518457237301991</v>
+        <v>-7.631250716972072</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.876577408347261</v>
       </c>
       <c r="E71">
-        <v>-12.42699063534251</v>
+        <v>-12.21865818861964</v>
       </c>
       <c r="F71">
-        <v>5.209765637336934</v>
+        <v>4.102018074064851</v>
       </c>
       <c r="G71">
-        <v>-6.333140406067672</v>
+        <v>-9.964635648204672</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.897457940933764</v>
       </c>
       <c r="E72">
-        <v>-13.62793288522868</v>
+        <v>-14.73453796458705</v>
       </c>
       <c r="F72">
-        <v>5.129269863337296</v>
+        <v>3.622131583744653</v>
       </c>
       <c r="G72">
-        <v>-6.574234722590992</v>
+        <v>-8.227268207137408</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.928001030843163</v>
       </c>
       <c r="E73">
-        <v>-13.14404279513906</v>
+        <v>-15.15322708591423</v>
       </c>
       <c r="F73">
-        <v>4.539503750505354</v>
+        <v>3.462301406844099</v>
       </c>
       <c r="G73">
-        <v>-6.609396292822002</v>
+        <v>-8.090372362455815</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.969774566403698</v>
       </c>
       <c r="E74">
-        <v>-13.24793051734903</v>
+        <v>-13.84567097246548</v>
       </c>
       <c r="F74">
-        <v>4.645153729058403</v>
+        <v>3.613962224418244</v>
       </c>
       <c r="G74">
-        <v>-5.936667123818408</v>
+        <v>-8.587638208568102</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.021593125380413</v>
       </c>
       <c r="E75">
-        <v>-12.46719442758261</v>
+        <v>-12.42406071265955</v>
       </c>
       <c r="F75">
-        <v>4.603980555669656</v>
+        <v>4.634896883876939</v>
       </c>
       <c r="G75">
-        <v>-6.853965422976772</v>
+        <v>-8.474340909342034</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.081244877184524</v>
       </c>
       <c r="E76">
-        <v>-12.56195727466712</v>
+        <v>-13.42388890339106</v>
       </c>
       <c r="F76">
-        <v>4.811474992927293</v>
+        <v>3.381426240573978</v>
       </c>
       <c r="G76">
-        <v>-6.574605500627209</v>
+        <v>-8.377623622655843</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.146172713713174</v>
       </c>
       <c r="E77">
-        <v>-12.82610316353453</v>
+        <v>-13.00421710320422</v>
       </c>
       <c r="F77">
-        <v>4.231526690553332</v>
+        <v>3.490623288345814</v>
       </c>
       <c r="G77">
-        <v>-6.531690403851232</v>
+        <v>-7.123796677917709</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.21341531631928</v>
       </c>
       <c r="E78">
-        <v>-14.00254184056519</v>
+        <v>-13.01281214687078</v>
       </c>
       <c r="F78">
-        <v>4.282123371516325</v>
+        <v>3.512719160448088</v>
       </c>
       <c r="G78">
-        <v>-6.820323058327786</v>
+        <v>-6.722578749293487</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.285262500075483</v>
       </c>
       <c r="E79">
-        <v>-14.82896570459499</v>
+        <v>-15.20491055976377</v>
       </c>
       <c r="F79">
-        <v>4.026550490200205</v>
+        <v>3.173201183267071</v>
       </c>
       <c r="G79">
-        <v>-5.328420520901022</v>
+        <v>-9.388197207084541</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.361827138375867</v>
       </c>
       <c r="E80">
-        <v>-15.53430723060771</v>
+        <v>-14.82455497091152</v>
       </c>
       <c r="F80">
-        <v>3.711633368147528</v>
+        <v>3.423939712420454</v>
       </c>
       <c r="G80">
-        <v>-4.312971041234988</v>
+        <v>-6.960788872066055</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.443487475952347</v>
       </c>
       <c r="E81">
-        <v>-15.56155053023785</v>
+        <v>-14.44546735478142</v>
       </c>
       <c r="F81">
-        <v>4.29199585422289</v>
+        <v>2.855215788354426</v>
       </c>
       <c r="G81">
-        <v>-5.447473082742355</v>
+        <v>-8.003049213094313</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.528102073511084</v>
       </c>
       <c r="E82">
-        <v>-17.019302541099</v>
+        <v>-16.40904538382534</v>
       </c>
       <c r="F82">
-        <v>4.093305305722206</v>
+        <v>3.122672428431108</v>
       </c>
       <c r="G82">
-        <v>-4.797056220342985</v>
+        <v>-7.382386467795987</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.617805973618786</v>
       </c>
       <c r="E83">
-        <v>-17.11118075024062</v>
+        <v>-16.07912793847052</v>
       </c>
       <c r="F83">
-        <v>4.556162218975651</v>
+        <v>2.623866026630968</v>
       </c>
       <c r="G83">
-        <v>-4.184304500224482</v>
+        <v>-7.018259467679729</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.714384832230811</v>
       </c>
       <c r="E84">
-        <v>-18.02724122877825</v>
+        <v>-16.77360112686483</v>
       </c>
       <c r="F84">
-        <v>3.903726798652317</v>
+        <v>3.064872264533369</v>
       </c>
       <c r="G84">
-        <v>-5.264889509067054</v>
+        <v>-8.997551374324852</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.821937383076838</v>
       </c>
       <c r="E85">
-        <v>-18.65991886086389</v>
+        <v>-19.80506125402754</v>
       </c>
       <c r="F85">
-        <v>4.08503322883785</v>
+        <v>2.884155631938629</v>
       </c>
       <c r="G85">
-        <v>-5.096602217726253</v>
+        <v>-5.629236351027795</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.942722070535805</v>
       </c>
       <c r="E86">
-        <v>-20.15523909209267</v>
+        <v>-19.01979216177944</v>
       </c>
       <c r="F86">
-        <v>3.714827552852723</v>
+        <v>2.268170034073278</v>
       </c>
       <c r="G86">
-        <v>-4.377430638770279</v>
+        <v>-7.984493905175652</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.0769694262131</v>
       </c>
       <c r="E87">
-        <v>-19.47434226877336</v>
+        <v>-21.96090017554111</v>
       </c>
       <c r="F87">
-        <v>3.963317892874907</v>
+        <v>2.750422341695871</v>
       </c>
       <c r="G87">
-        <v>-4.452301552313688</v>
+        <v>-6.046548671401093</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-10.22704991057547</v>
       </c>
       <c r="E88">
-        <v>-21.84141638884872</v>
+        <v>-21.47019926054396</v>
       </c>
       <c r="F88">
-        <v>3.37649414105771</v>
+        <v>2.892846862728801</v>
       </c>
       <c r="G88">
-        <v>-4.837543213164974</v>
+        <v>-6.444386941819086</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-10.3924514350512</v>
       </c>
       <c r="E89">
-        <v>-22.5342185703342</v>
+        <v>-22.35715523663429</v>
       </c>
       <c r="F89">
-        <v>4.043689411764126</v>
+        <v>2.672406699700214</v>
       </c>
       <c r="G89">
-        <v>-3.953598531158364</v>
+        <v>-7.148166310439705</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-10.57848192296898</v>
       </c>
       <c r="E90">
-        <v>-25.51654928298769</v>
+        <v>-26.61259848943418</v>
       </c>
       <c r="F90">
-        <v>3.395631084797184</v>
+        <v>2.347356987576493</v>
       </c>
       <c r="G90">
-        <v>-3.894920446010815</v>
+        <v>-5.122103871686257</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-10.7865464269215</v>
       </c>
       <c r="E91">
-        <v>-26.39962888532746</v>
+        <v>-26.71024144598757</v>
       </c>
       <c r="F91">
-        <v>3.268334209274178</v>
+        <v>2.084895402938692</v>
       </c>
       <c r="G91">
-        <v>-5.209085774005577</v>
+        <v>-5.287789154330418</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-11.01686859487611</v>
       </c>
       <c r="E92">
-        <v>-28.24101510022241</v>
+        <v>-27.2179875371496</v>
       </c>
       <c r="F92">
-        <v>3.240338704529166</v>
+        <v>2.419544236526054</v>
       </c>
       <c r="G92">
-        <v>-3.929012338013445</v>
+        <v>-5.055803508856117</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-11.26967849185867</v>
       </c>
       <c r="E93">
-        <v>-28.14807722816299</v>
+        <v>-28.53164803356068</v>
       </c>
       <c r="F93">
-        <v>3.085773630840806</v>
+        <v>1.604820044850656</v>
       </c>
       <c r="G93">
-        <v>-3.79709410643753</v>
+        <v>-6.494566663127674</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-11.54157427328628</v>
       </c>
       <c r="E94">
-        <v>-31.08278877238882</v>
+        <v>-31.29516061792654</v>
       </c>
       <c r="F94">
-        <v>3.140079741033536</v>
+        <v>1.814696866758744</v>
       </c>
       <c r="G94">
-        <v>-4.412569240450373</v>
+        <v>-7.181250867423586</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-11.83762795880588</v>
       </c>
       <c r="E95">
-        <v>-32.42986487850251</v>
+        <v>-32.86930573196983</v>
       </c>
       <c r="F95">
-        <v>2.776340300994662</v>
+        <v>1.184198271996345</v>
       </c>
       <c r="G95">
-        <v>-4.422373530469994</v>
+        <v>-5.873008144343621</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-12.15953114949909</v>
       </c>
       <c r="E96">
-        <v>-35.53095255777015</v>
+        <v>-35.55663806234165</v>
       </c>
       <c r="F96">
-        <v>2.246186819937784</v>
+        <v>0.7565635407099339</v>
       </c>
       <c r="G96">
-        <v>-3.844212448031156</v>
+        <v>-7.592358397827974</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-12.50291720501091</v>
       </c>
       <c r="E97">
-        <v>-37.83332610546092</v>
+        <v>-35.5553066909834</v>
       </c>
       <c r="F97">
-        <v>2.314160992276706</v>
+        <v>1.149539379863214</v>
       </c>
       <c r="G97">
-        <v>-3.954789614584443</v>
+        <v>-6.39519814942145</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-12.868399564746</v>
       </c>
       <c r="E98">
-        <v>-38.77590532778747</v>
+        <v>-41.50761217496045</v>
       </c>
       <c r="F98">
-        <v>1.697849017654651</v>
+        <v>0.07055935975555133</v>
       </c>
       <c r="G98">
-        <v>-4.732360374855414</v>
+        <v>-7.298088604712293</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-13.24222596910317</v>
       </c>
       <c r="E99">
-        <v>-41.31107866726456</v>
+        <v>-41.49966470307699</v>
       </c>
       <c r="F99">
-        <v>1.315736388621684</v>
+        <v>0.7856905953271701</v>
       </c>
       <c r="G99">
-        <v>-3.977807383823948</v>
+        <v>-4.848942176862485</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-13.63622791516693</v>
       </c>
       <c r="E100">
-        <v>-44.51523894342079</v>
+        <v>-43.73457078076449</v>
       </c>
       <c r="F100">
-        <v>1.541022500956649</v>
+        <v>0.4836844076145264</v>
       </c>
       <c r="G100">
-        <v>-4.249367842526711</v>
+        <v>-7.779699742764469</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-14.02024465340495</v>
       </c>
       <c r="E101">
-        <v>-46.10111506938095</v>
+        <v>-46.99980205738816</v>
       </c>
       <c r="F101">
-        <v>1.26194386621869</v>
+        <v>0.3094712874991651</v>
       </c>
       <c r="G101">
-        <v>-4.526949342791056</v>
+        <v>-8.710398550771608</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-14.43117535307559</v>
       </c>
       <c r="E102">
-        <v>-48.59071271432635</v>
+        <v>-48.50477925943829</v>
       </c>
       <c r="F102">
-        <v>0.9934600505625365</v>
+        <v>-0.5879405383236792</v>
       </c>
       <c r="G102">
-        <v>-4.886102011023196</v>
+        <v>-7.838702668846405</v>
       </c>
     </row>
   </sheetData>
